--- a/outputs/daily_schedule.xlsx
+++ b/outputs/daily_schedule.xlsx
@@ -14,9 +14,708 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="234">
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>Master PO List</t>
+  </si>
+  <si>
+    <t>NUM</t>
+  </si>
+  <si>
+    <t>PO DATE</t>
+  </si>
+  <si>
+    <t>Factory</t>
+  </si>
+  <si>
+    <t>PO#NO</t>
+  </si>
+  <si>
+    <t>sku</t>
+  </si>
+  <si>
+    <t>COLOR TOP</t>
+  </si>
+  <si>
+    <t>XFD</t>
+  </si>
+  <si>
+    <t>Customer RTA</t>
+  </si>
+  <si>
+    <t>QTY</t>
+  </si>
+  <si>
+    <t>Blc Del 1/24</t>
+  </si>
+  <si>
+    <t>Completion Date</t>
+  </si>
+  <si>
+    <t>Factory 5</t>
+  </si>
+  <si>
+    <t>PO090</t>
+  </si>
+  <si>
+    <t>SKU10</t>
+  </si>
+  <si>
+    <t>Color 6</t>
+  </si>
+  <si>
+    <t>2025-02-14</t>
+  </si>
+  <si>
+    <t>2025-05-02</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>Factory 1</t>
+  </si>
+  <si>
+    <t>PO051</t>
+  </si>
+  <si>
+    <t>SKU1</t>
+  </si>
+  <si>
+    <t>Color 2</t>
+  </si>
+  <si>
+    <t>2025-05-20</t>
+  </si>
+  <si>
+    <t>2025-03-04</t>
+  </si>
+  <si>
+    <t>Factory 3</t>
+  </si>
+  <si>
+    <t>PO018</t>
+  </si>
+  <si>
+    <t>SKU8</t>
+  </si>
+  <si>
+    <t>Color 4</t>
+  </si>
+  <si>
+    <t>2025-04-10</t>
+  </si>
+  <si>
+    <t>2025-03-05</t>
+  </si>
+  <si>
+    <t>PO028</t>
+  </si>
+  <si>
+    <t>Color 7</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>Factory 4</t>
+  </si>
+  <si>
+    <t>PO074</t>
+  </si>
+  <si>
+    <t>SKU4</t>
+  </si>
+  <si>
+    <t>2025-03-12</t>
+  </si>
+  <si>
+    <t>PO054</t>
+  </si>
+  <si>
+    <t>Color 5</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>PO046</t>
+  </si>
+  <si>
+    <t>SKU6</t>
+  </si>
+  <si>
+    <t>2025-03-15</t>
+  </si>
+  <si>
+    <t>PO041</t>
+  </si>
+  <si>
+    <t>2025-03-17</t>
+  </si>
+  <si>
+    <t>PO033</t>
+  </si>
+  <si>
+    <t>SKU3</t>
+  </si>
+  <si>
+    <t>2025-03-18</t>
+  </si>
+  <si>
+    <t>Factory 2</t>
+  </si>
+  <si>
+    <t>PO022</t>
+  </si>
+  <si>
+    <t>SKU2</t>
+  </si>
+  <si>
+    <t>Color 1</t>
+  </si>
+  <si>
+    <t>2025-03-21</t>
+  </si>
+  <si>
+    <t>PO058</t>
+  </si>
+  <si>
+    <t>PO062</t>
+  </si>
+  <si>
+    <t>2025-03-25</t>
+  </si>
+  <si>
+    <t>PO057</t>
+  </si>
+  <si>
+    <t>SKU7</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>PO065</t>
+  </si>
+  <si>
+    <t>SKU5</t>
+  </si>
+  <si>
+    <t>PO027</t>
+  </si>
+  <si>
+    <t>2025-03-31</t>
+  </si>
+  <si>
+    <t>PO004</t>
+  </si>
+  <si>
+    <t>2025-04-01</t>
+  </si>
+  <si>
+    <t>PO060</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>PO053</t>
+  </si>
+  <si>
+    <t>2025-02-30</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>PO068</t>
+  </si>
+  <si>
+    <t>2025-04-09</t>
+  </si>
+  <si>
+    <t>PO005</t>
+  </si>
+  <si>
+    <t>PO072</t>
+  </si>
+  <si>
+    <t>2025-04-12</t>
+  </si>
+  <si>
+    <t>PO047</t>
+  </si>
+  <si>
+    <t>2025-04-16</t>
+  </si>
+  <si>
+    <t>PO032</t>
+  </si>
+  <si>
+    <t>2025-04-17</t>
+  </si>
+  <si>
+    <t>PO038</t>
+  </si>
+  <si>
+    <t>Color 3</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>PO086</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>PO096</t>
+  </si>
+  <si>
+    <t>2025-04-22</t>
+  </si>
+  <si>
+    <t>PO095</t>
+  </si>
+  <si>
+    <t>2025-04-23</t>
+  </si>
+  <si>
+    <t>PO002</t>
+  </si>
+  <si>
+    <t>PO016</t>
+  </si>
+  <si>
+    <t>2025-04-28</t>
+  </si>
+  <si>
+    <t>PO063</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>PO030</t>
+  </si>
+  <si>
+    <t>PO031</t>
+  </si>
+  <si>
+    <t>2025-05-06</t>
+  </si>
+  <si>
+    <t>PO100</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>PO076</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>PO071</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>PO064</t>
+  </si>
+  <si>
+    <t>PO087</t>
+  </si>
+  <si>
+    <t>2025-05-17</t>
+  </si>
+  <si>
+    <t>PO036</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>PO001</t>
+  </si>
+  <si>
+    <t>PO017</t>
+  </si>
+  <si>
+    <t>2025-03-14</t>
+  </si>
+  <si>
+    <t>2025-05-22</t>
+  </si>
+  <si>
+    <t>PO035</t>
+  </si>
+  <si>
+    <t>2025-05-23</t>
+  </si>
+  <si>
+    <t>PO089</t>
+  </si>
+  <si>
+    <t>SKU9</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>PO015</t>
+  </si>
+  <si>
+    <t>2025-05-27</t>
+  </si>
+  <si>
+    <t>PO025</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>PO070</t>
+  </si>
+  <si>
+    <t>2025-05-31</t>
+  </si>
+  <si>
+    <t>PO021</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>PO048</t>
+  </si>
+  <si>
+    <t>2025-06-06</t>
+  </si>
+  <si>
+    <t>PO082</t>
+  </si>
+  <si>
+    <t>2025-06-10</t>
+  </si>
+  <si>
+    <t>PO099</t>
+  </si>
+  <si>
+    <t>2025-06-13</t>
+  </si>
+  <si>
+    <t>PO061</t>
+  </si>
+  <si>
+    <t>2025-06-14</t>
+  </si>
+  <si>
+    <t>PO085</t>
+  </si>
+  <si>
+    <t>2025-06-18</t>
+  </si>
+  <si>
+    <t>PO034</t>
+  </si>
+  <si>
+    <t>PO052</t>
+  </si>
+  <si>
+    <t>2025-06-19</t>
+  </si>
+  <si>
+    <t>PO029</t>
+  </si>
+  <si>
+    <t>2025-06-20</t>
+  </si>
+  <si>
+    <t>PO042</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>PO044</t>
+  </si>
+  <si>
+    <t>2025-06-24</t>
+  </si>
+  <si>
+    <t>PO055</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>2025-06-27</t>
+  </si>
+  <si>
+    <t>PO009</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>PO077</t>
+  </si>
+  <si>
+    <t>2025-07-01</t>
+  </si>
+  <si>
+    <t>PO040</t>
+  </si>
+  <si>
+    <t>2025-07-02</t>
+  </si>
+  <si>
+    <t>PO050</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>PO059</t>
+  </si>
+  <si>
+    <t>2025-07-05</t>
+  </si>
+  <si>
+    <t>PO011</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>PO083</t>
+  </si>
+  <si>
+    <t>2025-07-10</t>
+  </si>
+  <si>
+    <t>PO091</t>
+  </si>
+  <si>
+    <t>2025-07-12</t>
+  </si>
+  <si>
+    <t>PO014</t>
+  </si>
+  <si>
+    <t>2025-07-15</t>
+  </si>
+  <si>
+    <t>PO026</t>
+  </si>
+  <si>
+    <t>2025-07-16</t>
+  </si>
+  <si>
+    <t>PO092</t>
+  </si>
+  <si>
+    <t>2025-04-14</t>
+  </si>
+  <si>
+    <t>2025-07-18</t>
+  </si>
+  <si>
+    <t>PO088</t>
+  </si>
+  <si>
+    <t>2025-07-21</t>
+  </si>
+  <si>
+    <t>PO045</t>
+  </si>
+  <si>
+    <t>2025-07-22</t>
+  </si>
+  <si>
+    <t>PO024</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>PO084</t>
+  </si>
+  <si>
+    <t>2025-07-25</t>
+  </si>
+  <si>
+    <t>PO094</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>PO049</t>
+  </si>
+  <si>
+    <t>2025-07-30</t>
+  </si>
+  <si>
+    <t>PO080</t>
+  </si>
+  <si>
+    <t>2025-08-01</t>
+  </si>
+  <si>
+    <t>PO073</t>
+  </si>
+  <si>
+    <t>2025-08-04</t>
+  </si>
+  <si>
+    <t>PO006</t>
+  </si>
+  <si>
+    <t>2025-08-05</t>
+  </si>
+  <si>
+    <t>PO043</t>
+  </si>
+  <si>
+    <t>2025-08-07</t>
+  </si>
+  <si>
+    <t>PO081</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>PO037</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>PO010</t>
+  </si>
+  <si>
+    <t>2025-08-13</t>
+  </si>
+  <si>
+    <t>PO066</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>PO069</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>PO098</t>
+  </si>
+  <si>
+    <t>2025-08-19</t>
+  </si>
+  <si>
+    <t>PO097</t>
+  </si>
+  <si>
+    <t>2025-08-22</t>
+  </si>
+  <si>
+    <t>PO075</t>
+  </si>
+  <si>
+    <t>PO003</t>
+  </si>
+  <si>
+    <t>2025-08-25</t>
+  </si>
+  <si>
+    <t>PO023</t>
+  </si>
+  <si>
+    <t>2025-08-27</t>
+  </si>
+  <si>
+    <t>PO079</t>
+  </si>
+  <si>
+    <t>2025-04-30</t>
+  </si>
+  <si>
+    <t>2025-08-29</t>
+  </si>
+  <si>
+    <t>PO093</t>
+  </si>
+  <si>
+    <t>2025-09-01</t>
+  </si>
+  <si>
+    <t>PO007</t>
+  </si>
+  <si>
+    <t>2025-09-02</t>
+  </si>
+  <si>
+    <t>PO012</t>
+  </si>
+  <si>
+    <t>2025-09-05</t>
+  </si>
+  <si>
+    <t>PO056</t>
+  </si>
+  <si>
+    <t>2025-09-08</t>
+  </si>
+  <si>
+    <t>PO078</t>
+  </si>
+  <si>
+    <t>2025-09-11</t>
+  </si>
+  <si>
+    <t>PO039</t>
+  </si>
+  <si>
+    <t>2025-09-12</t>
+  </si>
+  <si>
+    <t>PO019</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>PO008</t>
+  </si>
+  <si>
+    <t>PO067</t>
+  </si>
+  <si>
+    <t>2025-09-16</t>
+  </si>
+  <si>
+    <t>PO020</t>
+  </si>
+  <si>
+    <t>2025-09-19</t>
+  </si>
+  <si>
+    <t>PO013</t>
   </si>
 </sst>
 </file>
@@ -44,12 +743,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -115,21 +820,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -424,77 +1130,77 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T177"/>
+  <dimension ref="A1:AD177"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:30">
       <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3">
         <v>4</v>
       </c>
-      <c r="C1" s="2">
+      <c r="C1" s="3">
         <v>4.5</v>
       </c>
-      <c r="D1" s="2">
+      <c r="D1" s="3">
         <v>5</v>
       </c>
-      <c r="E1" s="2">
+      <c r="E1" s="3">
         <v>5.5</v>
       </c>
-      <c r="F1" s="2">
+      <c r="F1" s="3">
         <v>6</v>
       </c>
-      <c r="G1" s="2">
+      <c r="G1" s="3">
         <v>6.5</v>
       </c>
-      <c r="H1" s="2">
+      <c r="H1" s="3">
         <v>7</v>
       </c>
-      <c r="I1" s="2">
+      <c r="I1" s="3">
         <v>7.5</v>
       </c>
-      <c r="J1" s="2">
+      <c r="J1" s="3">
         <v>8</v>
       </c>
-      <c r="K1" s="2">
+      <c r="K1" s="3">
         <v>8.5</v>
       </c>
-      <c r="L1" s="2">
+      <c r="L1" s="3">
         <v>9</v>
       </c>
-      <c r="M1" s="2">
+      <c r="M1" s="3">
         <v>9.5</v>
       </c>
-      <c r="N1" s="2">
+      <c r="N1" s="3">
         <v>10</v>
       </c>
-      <c r="O1" s="2">
+      <c r="O1" s="3">
         <v>10.5</v>
       </c>
-      <c r="P1" s="2">
+      <c r="P1" s="3">
         <v>11</v>
       </c>
-      <c r="Q1" s="2">
+      <c r="Q1" s="3">
         <v>11.5</v>
       </c>
-      <c r="R1" s="2">
+      <c r="R1" s="3">
         <v>12</v>
       </c>
-      <c r="S1" s="2">
+      <c r="S1" s="3">
         <v>12.5</v>
       </c>
-      <c r="T1" s="2">
+      <c r="T1" s="3">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
-      <c r="A2" s="3">
-        <v>45715</v>
+    <row r="2" spans="1:30">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="B2" s="4">
         <v>100</v>
@@ -553,10 +1259,40 @@
       <c r="T2" s="4">
         <v>350</v>
       </c>
-    </row>
-    <row r="3" spans="1:20">
-      <c r="A3" s="3">
-        <v>45716</v>
+      <c r="U2" s="2">
+        <v>9</v>
+      </c>
+      <c r="V2" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="W2" s="2">
+        <v>10</v>
+      </c>
+      <c r="X2" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>11</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>12</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>13</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30">
+      <c r="A3" s="1">
+        <v>71</v>
       </c>
       <c r="B3" s="4">
         <v>100</v>
@@ -615,10 +1351,40 @@
       <c r="T3" s="4">
         <v>350</v>
       </c>
-    </row>
-    <row r="4" spans="1:20">
-      <c r="A4" s="3">
-        <v>45717</v>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30">
+      <c r="A4" s="1">
+        <v>41</v>
       </c>
       <c r="B4" s="4">
         <v>100</v>
@@ -677,10 +1443,40 @@
       <c r="T4" s="4">
         <v>350</v>
       </c>
-    </row>
-    <row r="5" spans="1:20">
-      <c r="A5" s="3">
-        <v>45719</v>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30">
+      <c r="A5" s="1">
+        <v>42</v>
       </c>
       <c r="B5" s="4">
         <v>100</v>
@@ -739,10 +1535,40 @@
       <c r="T5" s="4">
         <v>350</v>
       </c>
-    </row>
-    <row r="6" spans="1:20">
-      <c r="A6" s="3">
-        <v>45720</v>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30">
+      <c r="A6" s="1">
+        <v>28</v>
       </c>
       <c r="B6" s="4">
         <v>100</v>
@@ -801,10 +1627,40 @@
       <c r="T6" s="4">
         <v>350</v>
       </c>
-    </row>
-    <row r="7" spans="1:20">
-      <c r="A7" s="3">
-        <v>45721</v>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30">
+      <c r="A7" s="1">
+        <v>44</v>
       </c>
       <c r="B7" s="4">
         <v>100</v>
@@ -863,10 +1719,40 @@
       <c r="T7" s="4">
         <v>350</v>
       </c>
-    </row>
-    <row r="8" spans="1:20">
-      <c r="A8" s="3">
-        <v>45722</v>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30">
+      <c r="A8" s="1">
+        <v>55</v>
       </c>
       <c r="B8" s="4">
         <v>100</v>
@@ -925,10 +1811,40 @@
       <c r="T8" s="4">
         <v>350</v>
       </c>
-    </row>
-    <row r="9" spans="1:20">
-      <c r="A9" s="3">
-        <v>45723</v>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30">
+      <c r="A9" s="1">
+        <v>63</v>
       </c>
       <c r="B9" s="4">
         <v>100</v>
@@ -987,10 +1903,40 @@
       <c r="T9" s="5">
         <v>350</v>
       </c>
-    </row>
-    <row r="10" spans="1:20">
-      <c r="A10" s="3">
-        <v>45724</v>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30">
+      <c r="A10" s="1">
+        <v>66</v>
       </c>
       <c r="B10" s="4">
         <v>100</v>
@@ -1049,10 +1995,40 @@
       <c r="T10" s="5">
         <v>350</v>
       </c>
-    </row>
-    <row r="11" spans="1:20">
-      <c r="A11" s="3">
-        <v>45726</v>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30">
+      <c r="A11" s="1">
+        <v>15</v>
       </c>
       <c r="B11" s="4">
         <v>100</v>
@@ -1111,10 +2087,40 @@
       <c r="T11" s="5">
         <v>350</v>
       </c>
-    </row>
-    <row r="12" spans="1:20">
-      <c r="A12" s="3">
-        <v>45727</v>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30">
+      <c r="A12" s="1">
+        <v>79</v>
       </c>
       <c r="B12" s="4">
         <v>100</v>
@@ -1173,10 +2179,40 @@
       <c r="T12" s="5">
         <v>350</v>
       </c>
-    </row>
-    <row r="13" spans="1:20">
-      <c r="A13" s="3">
-        <v>45728</v>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30">
+      <c r="A13" s="1">
+        <v>39</v>
       </c>
       <c r="B13" s="4">
         <v>100</v>
@@ -1235,10 +2271,40 @@
       <c r="T13" s="5">
         <v>350</v>
       </c>
-    </row>
-    <row r="14" spans="1:20">
-      <c r="A14" s="3">
-        <v>45729</v>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30">
+      <c r="A14" s="1">
+        <v>2</v>
       </c>
       <c r="B14" s="4">
         <v>100</v>
@@ -1297,10 +2363,40 @@
       <c r="T14" s="5">
         <v>350</v>
       </c>
-    </row>
-    <row r="15" spans="1:20">
-      <c r="A15" s="3">
-        <v>45730</v>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30">
+      <c r="A15" s="1">
+        <v>98</v>
       </c>
       <c r="B15" s="4">
         <v>100</v>
@@ -1359,10 +2455,40 @@
       <c r="T15" s="5">
         <v>350</v>
       </c>
-    </row>
-    <row r="16" spans="1:20">
-      <c r="A16" s="3">
-        <v>45731</v>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30">
+      <c r="A16" s="1">
+        <v>4</v>
       </c>
       <c r="B16" s="4">
         <v>100</v>
@@ -1421,10 +2547,40 @@
       <c r="T16" s="5">
         <v>350</v>
       </c>
-    </row>
-    <row r="17" spans="1:20">
-      <c r="A17" s="3">
-        <v>45733</v>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30">
+      <c r="A17" s="1">
+        <v>87</v>
       </c>
       <c r="B17" s="4">
         <v>100</v>
@@ -1483,10 +2639,40 @@
       <c r="T17" s="5">
         <v>350</v>
       </c>
-    </row>
-    <row r="18" spans="1:20">
-      <c r="A18" s="3">
-        <v>45734</v>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30">
+      <c r="A18" s="1">
+        <v>90</v>
       </c>
       <c r="B18" s="4">
         <v>100</v>
@@ -1545,10 +2731,40 @@
       <c r="T18" s="5">
         <v>350</v>
       </c>
-    </row>
-    <row r="19" spans="1:20">
-      <c r="A19" s="3">
-        <v>45735</v>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30">
+      <c r="A19" s="1">
+        <v>83</v>
       </c>
       <c r="B19" s="4">
         <v>100</v>
@@ -1607,10 +2823,40 @@
       <c r="T19" s="5">
         <v>350</v>
       </c>
-    </row>
-    <row r="20" spans="1:20">
-      <c r="A20" s="3">
-        <v>45736</v>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30">
+      <c r="A20" s="1">
+        <v>78</v>
       </c>
       <c r="B20" s="4">
         <v>100</v>
@@ -1669,10 +2915,40 @@
       <c r="T20" s="5">
         <v>350</v>
       </c>
-    </row>
-    <row r="21" spans="1:20">
-      <c r="A21" s="3">
-        <v>45737</v>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30">
+      <c r="A21" s="1">
+        <v>96</v>
       </c>
       <c r="B21" s="4">
         <v>100</v>
@@ -1731,10 +3007,40 @@
       <c r="T21" s="6">
         <v>350</v>
       </c>
-    </row>
-    <row r="22" spans="1:20">
-      <c r="A22" s="3">
-        <v>45738</v>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30">
+      <c r="A22" s="1">
+        <v>45</v>
       </c>
       <c r="B22" s="4">
         <v>100</v>
@@ -1793,10 +3099,40 @@
       <c r="T22" s="6">
         <v>350</v>
       </c>
-    </row>
-    <row r="23" spans="1:20">
-      <c r="A23" s="3">
-        <v>45740</v>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30">
+      <c r="A23" s="1">
+        <v>48</v>
       </c>
       <c r="B23" s="4">
         <v>100</v>
@@ -1855,10 +3191,40 @@
       <c r="T23" s="6">
         <v>350</v>
       </c>
-    </row>
-    <row r="24" spans="1:20">
-      <c r="A24" s="3">
-        <v>45741</v>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30">
+      <c r="A24" s="1">
+        <v>49</v>
       </c>
       <c r="B24" s="4">
         <v>100</v>
@@ -1917,10 +3283,40 @@
       <c r="T24" s="6">
         <v>350</v>
       </c>
-    </row>
-    <row r="25" spans="1:20">
-      <c r="A25" s="3">
-        <v>45742</v>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30">
+      <c r="A25" s="1">
+        <v>54</v>
       </c>
       <c r="B25" s="4">
         <v>100</v>
@@ -1979,10 +3375,40 @@
       <c r="T25" s="6">
         <v>350</v>
       </c>
-    </row>
-    <row r="26" spans="1:20">
-      <c r="A26" s="3">
-        <v>45743</v>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30">
+      <c r="A26" s="1">
+        <v>95</v>
       </c>
       <c r="B26" s="4">
         <v>100</v>
@@ -2041,10 +3467,40 @@
       <c r="T26" s="6">
         <v>350</v>
       </c>
-    </row>
-    <row r="27" spans="1:20">
-      <c r="A27" s="3">
-        <v>45744</v>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30">
+      <c r="A27" s="1">
+        <v>57</v>
       </c>
       <c r="B27" s="4">
         <v>100</v>
@@ -2103,10 +3559,40 @@
       <c r="T27" s="6">
         <v>350</v>
       </c>
-    </row>
-    <row r="28" spans="1:20">
-      <c r="A28" s="3">
-        <v>45745</v>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30">
+      <c r="A28" s="1">
+        <v>60</v>
       </c>
       <c r="B28" s="4">
         <v>100</v>
@@ -2165,10 +3651,40 @@
       <c r="T28" s="6">
         <v>350</v>
       </c>
-    </row>
-    <row r="29" spans="1:20">
-      <c r="A29" s="3">
-        <v>45747</v>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30">
+      <c r="A29" s="1">
+        <v>40</v>
       </c>
       <c r="B29" s="4">
         <v>100</v>
@@ -2227,10 +3743,40 @@
       <c r="T29" s="6">
         <v>350</v>
       </c>
-    </row>
-    <row r="30" spans="1:20">
-      <c r="A30" s="3">
-        <v>45748</v>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30">
+      <c r="A30" s="1">
+        <v>84</v>
       </c>
       <c r="B30" s="4">
         <v>100</v>
@@ -2289,10 +3835,40 @@
       <c r="T30" s="7">
         <v>350</v>
       </c>
-    </row>
-    <row r="31" spans="1:20">
-      <c r="A31" s="3">
-        <v>45749</v>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30">
+      <c r="A31" s="1">
+        <v>74</v>
       </c>
       <c r="B31" s="4">
         <v>100</v>
@@ -2351,10 +3927,40 @@
       <c r="T31" s="7">
         <v>350</v>
       </c>
-    </row>
-    <row r="32" spans="1:20">
-      <c r="A32" s="3">
-        <v>45750</v>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30">
+      <c r="A32" s="1">
+        <v>76</v>
       </c>
       <c r="B32" s="5">
         <v>100</v>
@@ -2413,10 +4019,40 @@
       <c r="T32" s="7">
         <v>350</v>
       </c>
-    </row>
-    <row r="33" spans="1:20">
-      <c r="A33" s="3">
-        <v>45751</v>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30">
+      <c r="A33" s="1">
+        <v>52</v>
       </c>
       <c r="B33" s="5">
         <v>100</v>
@@ -2475,10 +4111,40 @@
       <c r="T33" s="7">
         <v>350</v>
       </c>
-    </row>
-    <row r="34" spans="1:20">
-      <c r="A34" s="3">
-        <v>45752</v>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30">
+      <c r="A34" s="1">
+        <v>50</v>
       </c>
       <c r="B34" s="5">
         <v>100</v>
@@ -2537,10 +4203,40 @@
       <c r="T34" s="7">
         <v>350</v>
       </c>
-    </row>
-    <row r="35" spans="1:20">
-      <c r="A35" s="3">
-        <v>45754</v>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30">
+      <c r="A35" s="1">
+        <v>100</v>
       </c>
       <c r="B35" s="5">
         <v>100</v>
@@ -2599,10 +4295,40 @@
       <c r="T35" s="8">
         <v>350</v>
       </c>
-    </row>
-    <row r="36" spans="1:20">
-      <c r="A36" s="3">
-        <v>45755</v>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30">
+      <c r="A36" s="1">
+        <v>33</v>
       </c>
       <c r="B36" s="5">
         <v>100</v>
@@ -2661,10 +4387,40 @@
       <c r="T36" s="8">
         <v>350</v>
       </c>
-    </row>
-    <row r="37" spans="1:20">
-      <c r="A37" s="3">
-        <v>45756</v>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30">
+      <c r="A37" s="1">
+        <v>12</v>
       </c>
       <c r="B37" s="5">
         <v>100</v>
@@ -2723,10 +4479,40 @@
       <c r="T37" s="8">
         <v>350</v>
       </c>
-    </row>
-    <row r="38" spans="1:20">
-      <c r="A38" s="3">
-        <v>45757</v>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <v>0</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30">
+      <c r="A38" s="1">
+        <v>11</v>
       </c>
       <c r="B38" s="5">
         <v>100</v>
@@ -2785,10 +4571,40 @@
       <c r="T38" s="8">
         <v>350</v>
       </c>
-    </row>
-    <row r="39" spans="1:20">
-      <c r="A39" s="3">
-        <v>45758</v>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30">
+      <c r="A39" s="1">
+        <v>31</v>
       </c>
       <c r="B39" s="5">
         <v>100</v>
@@ -2847,10 +4663,40 @@
       <c r="T39" s="8">
         <v>350</v>
       </c>
-    </row>
-    <row r="40" spans="1:20">
-      <c r="A40" s="3">
-        <v>45759</v>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30">
+      <c r="A40" s="1">
+        <v>10</v>
       </c>
       <c r="B40" s="5">
         <v>100</v>
@@ -2909,10 +4755,40 @@
       <c r="T40" s="8">
         <v>350</v>
       </c>
-    </row>
-    <row r="41" spans="1:20">
-      <c r="A41" s="3">
-        <v>45761</v>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>0</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30">
+      <c r="A41" s="1">
+        <v>17</v>
       </c>
       <c r="B41" s="5">
         <v>100</v>
@@ -2971,10 +4847,40 @@
       <c r="T41" s="8">
         <v>350</v>
       </c>
-    </row>
-    <row r="42" spans="1:20">
-      <c r="A42" s="3">
-        <v>45762</v>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+      <c r="AA41">
+        <v>0</v>
+      </c>
+      <c r="AB41">
+        <v>0</v>
+      </c>
+      <c r="AC41">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:30">
+      <c r="A42" s="1">
+        <v>67</v>
       </c>
       <c r="B42" s="5">
         <v>100</v>
@@ -3033,10 +4939,40 @@
       <c r="T42" s="8">
         <v>350</v>
       </c>
-    </row>
-    <row r="43" spans="1:20">
-      <c r="A43" s="3">
-        <v>45763</v>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="43" spans="1:30">
+      <c r="A43" s="1">
+        <v>75</v>
       </c>
       <c r="B43" s="5">
         <v>100</v>
@@ -3095,10 +5031,40 @@
       <c r="T43" s="8">
         <v>350</v>
       </c>
-    </row>
-    <row r="44" spans="1:20">
-      <c r="A44" s="3">
-        <v>45764</v>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+      <c r="AA43">
+        <v>0</v>
+      </c>
+      <c r="AB43">
+        <v>0</v>
+      </c>
+      <c r="AC43">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="44" spans="1:30">
+      <c r="A44" s="1">
+        <v>81</v>
       </c>
       <c r="B44" s="5">
         <v>100</v>
@@ -3157,10 +5123,40 @@
       <c r="T44" s="8">
         <v>350</v>
       </c>
-    </row>
-    <row r="45" spans="1:20">
-      <c r="A45" s="3">
-        <v>45765</v>
+      <c r="U44">
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+      <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+      <c r="AA44">
+        <v>0</v>
+      </c>
+      <c r="AB44">
+        <v>0</v>
+      </c>
+      <c r="AC44">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="45" spans="1:30">
+      <c r="A45" s="1">
+        <v>86</v>
       </c>
       <c r="B45" s="5">
         <v>100</v>
@@ -3219,10 +5215,40 @@
       <c r="T45" s="9">
         <v>350</v>
       </c>
-    </row>
-    <row r="46" spans="1:20">
-      <c r="A46" s="3">
-        <v>45766</v>
+      <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <v>0</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+      <c r="AA45">
+        <v>0</v>
+      </c>
+      <c r="AB45">
+        <v>0</v>
+      </c>
+      <c r="AC45">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30">
+      <c r="A46" s="1">
+        <v>88</v>
       </c>
       <c r="B46" s="5">
         <v>100</v>
@@ -3281,10 +5307,40 @@
       <c r="T46" s="9">
         <v>350</v>
       </c>
-    </row>
-    <row r="47" spans="1:20">
-      <c r="A47" s="3">
-        <v>45768</v>
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
+        <v>0</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+      <c r="AA46">
+        <v>0</v>
+      </c>
+      <c r="AB46">
+        <v>0</v>
+      </c>
+      <c r="AC46">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30">
+      <c r="A47" s="1">
+        <v>89</v>
       </c>
       <c r="B47" s="5">
         <v>100</v>
@@ -3343,10 +5399,40 @@
       <c r="T47" s="9">
         <v>350</v>
       </c>
-    </row>
-    <row r="48" spans="1:20">
-      <c r="A48" s="3">
-        <v>45769</v>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+      <c r="AA47">
+        <v>0</v>
+      </c>
+      <c r="AB47">
+        <v>0</v>
+      </c>
+      <c r="AC47">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="48" spans="1:30">
+      <c r="A48" s="1">
+        <v>93</v>
       </c>
       <c r="B48" s="5">
         <v>100</v>
@@ -3405,10 +5491,40 @@
       <c r="T48" s="9">
         <v>350</v>
       </c>
-    </row>
-    <row r="49" spans="1:20">
-      <c r="A49" s="3">
-        <v>45770</v>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+      <c r="AA48">
+        <v>0</v>
+      </c>
+      <c r="AB48">
+        <v>0</v>
+      </c>
+      <c r="AC48">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="49" spans="1:30">
+      <c r="A49" s="1">
+        <v>5</v>
       </c>
       <c r="B49" s="5">
         <v>100</v>
@@ -3467,10 +5583,40 @@
       <c r="T49" s="9">
         <v>350</v>
       </c>
-    </row>
-    <row r="50" spans="1:20">
-      <c r="A50" s="3">
-        <v>45771</v>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="50" spans="1:30">
+      <c r="A50" s="1">
+        <v>97</v>
       </c>
       <c r="B50" s="5">
         <v>100</v>
@@ -3529,10 +5675,40 @@
       <c r="T50" s="9">
         <v>350</v>
       </c>
-    </row>
-    <row r="51" spans="1:20">
-      <c r="A51" s="3">
-        <v>45772</v>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+      <c r="AA50">
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <v>0</v>
+      </c>
+      <c r="AC50">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="51" spans="1:30">
+      <c r="A51" s="1">
+        <v>3</v>
       </c>
       <c r="B51" s="5">
         <v>100</v>
@@ -3591,10 +5767,40 @@
       <c r="T51" s="9">
         <v>350</v>
       </c>
-    </row>
-    <row r="52" spans="1:20">
-      <c r="A52" s="3">
-        <v>45773</v>
+      <c r="U51">
+        <v>0</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+      <c r="AA51">
+        <v>0</v>
+      </c>
+      <c r="AB51">
+        <v>0</v>
+      </c>
+      <c r="AC51">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="52" spans="1:30">
+      <c r="A52" s="1">
+        <v>85</v>
       </c>
       <c r="B52" s="5">
         <v>100</v>
@@ -3653,10 +5859,40 @@
       <c r="T52" s="9">
         <v>172</v>
       </c>
-    </row>
-    <row r="53" spans="1:20">
-      <c r="A53" s="3">
-        <v>45775</v>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0</v>
+      </c>
+      <c r="X52">
+        <v>0</v>
+      </c>
+      <c r="Y52">
+        <v>0</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+      <c r="AA52">
+        <v>0</v>
+      </c>
+      <c r="AB52">
+        <v>0</v>
+      </c>
+      <c r="AC52">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="53" spans="1:30">
+      <c r="A53" s="1">
+        <v>19</v>
       </c>
       <c r="B53" s="5">
         <v>100</v>
@@ -3715,10 +5951,40 @@
       <c r="T53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:20">
-      <c r="A54" s="3">
-        <v>45776</v>
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0</v>
+      </c>
+      <c r="X53">
+        <v>0</v>
+      </c>
+      <c r="Y53">
+        <v>0</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+      <c r="AA53">
+        <v>0</v>
+      </c>
+      <c r="AB53">
+        <v>0</v>
+      </c>
+      <c r="AC53">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="54" spans="1:30">
+      <c r="A54" s="1">
+        <v>1</v>
       </c>
       <c r="B54" s="5">
         <v>100</v>
@@ -3777,10 +6043,40 @@
       <c r="T54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:20">
-      <c r="A55" s="3">
-        <v>45777</v>
+      <c r="U54">
+        <v>0</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0</v>
+      </c>
+      <c r="X54">
+        <v>0</v>
+      </c>
+      <c r="Y54">
+        <v>0</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+      <c r="AA54">
+        <v>0</v>
+      </c>
+      <c r="AB54">
+        <v>0</v>
+      </c>
+      <c r="AC54">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="55" spans="1:30">
+      <c r="A55" s="1">
+        <v>36</v>
       </c>
       <c r="B55" s="5">
         <v>100</v>
@@ -3839,10 +6135,40 @@
       <c r="T55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:20">
-      <c r="A56" s="3">
-        <v>45778</v>
+      <c r="U55">
+        <v>0</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0</v>
+      </c>
+      <c r="X55">
+        <v>0</v>
+      </c>
+      <c r="Y55">
+        <v>0</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+      <c r="AA55">
+        <v>0</v>
+      </c>
+      <c r="AB55">
+        <v>0</v>
+      </c>
+      <c r="AC55">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30">
+      <c r="A56" s="1">
+        <v>25</v>
       </c>
       <c r="B56" s="5">
         <v>100</v>
@@ -3901,10 +6227,40 @@
       <c r="T56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:20">
-      <c r="A57" s="3">
-        <v>45779</v>
+      <c r="U56">
+        <v>0</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>0</v>
+      </c>
+      <c r="X56">
+        <v>0</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+      <c r="AA56">
+        <v>0</v>
+      </c>
+      <c r="AB56">
+        <v>0</v>
+      </c>
+      <c r="AC56">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30">
+      <c r="A57" s="1">
+        <v>99</v>
       </c>
       <c r="B57" s="5">
         <v>100</v>
@@ -3963,10 +6319,40 @@
       <c r="T57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:20">
-      <c r="A58" s="3">
-        <v>45780</v>
+      <c r="U57">
+        <v>0</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0</v>
+      </c>
+      <c r="X57">
+        <v>0</v>
+      </c>
+      <c r="Y57">
+        <v>0</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+      <c r="AA57">
+        <v>0</v>
+      </c>
+      <c r="AB57">
+        <v>0</v>
+      </c>
+      <c r="AC57">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="58" spans="1:30">
+      <c r="A58" s="1">
+        <v>27</v>
       </c>
       <c r="B58" s="5">
         <v>100</v>
@@ -4025,10 +6411,40 @@
       <c r="T58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:20">
-      <c r="A59" s="3">
-        <v>45782</v>
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0</v>
+      </c>
+      <c r="X58">
+        <v>0</v>
+      </c>
+      <c r="Y58">
+        <v>0</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+      <c r="AA58">
+        <v>0</v>
+      </c>
+      <c r="AB58">
+        <v>0</v>
+      </c>
+      <c r="AC58">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="59" spans="1:30">
+      <c r="A59" s="1">
+        <v>30</v>
       </c>
       <c r="B59" s="5">
         <v>100</v>
@@ -4087,10 +6503,40 @@
       <c r="T59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:20">
-      <c r="A60" s="3">
-        <v>45783</v>
+      <c r="U59">
+        <v>0</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0</v>
+      </c>
+      <c r="X59">
+        <v>0</v>
+      </c>
+      <c r="Y59">
+        <v>0</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+      <c r="AA59">
+        <v>0</v>
+      </c>
+      <c r="AB59">
+        <v>0</v>
+      </c>
+      <c r="AC59">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30">
+      <c r="A60" s="1">
+        <v>37</v>
       </c>
       <c r="B60" s="5">
         <v>100</v>
@@ -4149,10 +6595,40 @@
       <c r="T60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:20">
-      <c r="A61" s="3">
-        <v>45784</v>
+      <c r="U60">
+        <v>0</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>0</v>
+      </c>
+      <c r="X60">
+        <v>0</v>
+      </c>
+      <c r="Y60">
+        <v>0</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+      <c r="AA60">
+        <v>0</v>
+      </c>
+      <c r="AB60">
+        <v>0</v>
+      </c>
+      <c r="AC60">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="61" spans="1:30">
+      <c r="A61" s="1">
+        <v>6</v>
       </c>
       <c r="B61" s="5">
         <v>100</v>
@@ -4211,10 +6687,40 @@
       <c r="T61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:20">
-      <c r="A62" s="3">
-        <v>45785</v>
+      <c r="U61">
+        <v>0</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61">
+        <v>0</v>
+      </c>
+      <c r="X61">
+        <v>0</v>
+      </c>
+      <c r="Y61">
+        <v>0</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+      <c r="AA61">
+        <v>0</v>
+      </c>
+      <c r="AB61">
+        <v>0</v>
+      </c>
+      <c r="AC61">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="62" spans="1:30">
+      <c r="A62" s="1">
+        <v>20</v>
       </c>
       <c r="B62" s="5">
         <v>100</v>
@@ -4273,10 +6779,40 @@
       <c r="T62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:20">
-      <c r="A63" s="3">
-        <v>45786</v>
+      <c r="U62">
+        <v>0</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>0</v>
+      </c>
+      <c r="X62">
+        <v>0</v>
+      </c>
+      <c r="Y62">
+        <v>0</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+      <c r="AA62">
+        <v>0</v>
+      </c>
+      <c r="AB62">
+        <v>0</v>
+      </c>
+      <c r="AC62">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="63" spans="1:30">
+      <c r="A63" s="1">
+        <v>47</v>
       </c>
       <c r="B63" s="5">
         <v>100</v>
@@ -4335,10 +6871,40 @@
       <c r="T63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:20">
-      <c r="A64" s="3">
-        <v>45787</v>
+      <c r="U63">
+        <v>0</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0</v>
+      </c>
+      <c r="X63">
+        <v>0</v>
+      </c>
+      <c r="Y63">
+        <v>0</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+      <c r="AA63">
+        <v>0</v>
+      </c>
+      <c r="AB63">
+        <v>0</v>
+      </c>
+      <c r="AC63">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="64" spans="1:30">
+      <c r="A64" s="1">
+        <v>73</v>
       </c>
       <c r="B64" s="5">
         <v>100</v>
@@ -4397,10 +6963,40 @@
       <c r="T64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:20">
-      <c r="A65" s="3">
-        <v>45789</v>
+      <c r="U64">
+        <v>0</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0</v>
+      </c>
+      <c r="X64">
+        <v>0</v>
+      </c>
+      <c r="Y64">
+        <v>0</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+      <c r="AA64">
+        <v>0</v>
+      </c>
+      <c r="AB64">
+        <v>0</v>
+      </c>
+      <c r="AC64">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="65" spans="1:30">
+      <c r="A65" s="1">
+        <v>46</v>
       </c>
       <c r="B65" s="5">
         <v>100</v>
@@ -4459,10 +7055,40 @@
       <c r="T65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:20">
-      <c r="A66" s="3">
-        <v>45790</v>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <v>0</v>
+      </c>
+      <c r="Y65">
+        <v>0</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+      <c r="AA65">
+        <v>0</v>
+      </c>
+      <c r="AB65">
+        <v>0</v>
+      </c>
+      <c r="AC65">
+        <v>0</v>
+      </c>
+      <c r="AD65" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="66" spans="1:30">
+      <c r="A66" s="1">
+        <v>61</v>
       </c>
       <c r="B66" s="5">
         <v>100</v>
@@ -4521,10 +7147,40 @@
       <c r="T66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:20">
-      <c r="A67" s="3">
-        <v>45791</v>
+      <c r="U66">
+        <v>0</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0</v>
+      </c>
+      <c r="X66">
+        <v>0</v>
+      </c>
+      <c r="Y66">
+        <v>0</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+      <c r="AA66">
+        <v>0</v>
+      </c>
+      <c r="AB66">
+        <v>0</v>
+      </c>
+      <c r="AC66">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="67" spans="1:30">
+      <c r="A67" s="1">
+        <v>16</v>
       </c>
       <c r="B67" s="5">
         <v>100</v>
@@ -4583,10 +7239,40 @@
       <c r="T67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:20">
-      <c r="A68" s="3">
-        <v>45792</v>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0</v>
+      </c>
+      <c r="X67">
+        <v>0</v>
+      </c>
+      <c r="Y67">
+        <v>0</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+      <c r="AA67">
+        <v>0</v>
+      </c>
+      <c r="AB67">
+        <v>0</v>
+      </c>
+      <c r="AC67">
+        <v>0</v>
+      </c>
+      <c r="AD67" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="68" spans="1:30">
+      <c r="A68" s="1">
+        <v>80</v>
       </c>
       <c r="B68" s="5">
         <v>100</v>
@@ -4645,10 +7331,40 @@
       <c r="T68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:20">
-      <c r="A69" s="3">
-        <v>45793</v>
+      <c r="U68">
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0</v>
+      </c>
+      <c r="X68">
+        <v>0</v>
+      </c>
+      <c r="Y68">
+        <v>0</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+      <c r="AA68">
+        <v>0</v>
+      </c>
+      <c r="AB68">
+        <v>0</v>
+      </c>
+      <c r="AC68">
+        <v>0</v>
+      </c>
+      <c r="AD68" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="69" spans="1:30">
+      <c r="A69" s="1">
+        <v>43</v>
       </c>
       <c r="B69" s="6">
         <v>100</v>
@@ -4707,10 +7423,40 @@
       <c r="T69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:20">
-      <c r="A70" s="3">
-        <v>45794</v>
+      <c r="U69">
+        <v>0</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>0</v>
+      </c>
+      <c r="X69">
+        <v>0</v>
+      </c>
+      <c r="Y69">
+        <v>0</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+      <c r="AA69">
+        <v>0</v>
+      </c>
+      <c r="AB69">
+        <v>0</v>
+      </c>
+      <c r="AC69">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="70" spans="1:30">
+      <c r="A70" s="1">
+        <v>26</v>
       </c>
       <c r="B70" s="6">
         <v>100</v>
@@ -4769,10 +7515,40 @@
       <c r="T70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:20">
-      <c r="A71" s="3">
-        <v>45796</v>
+      <c r="U70">
+        <v>0</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <v>0</v>
+      </c>
+      <c r="X70">
+        <v>0</v>
+      </c>
+      <c r="Y70">
+        <v>0</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+      <c r="AA70">
+        <v>0</v>
+      </c>
+      <c r="AB70">
+        <v>0</v>
+      </c>
+      <c r="AC70">
+        <v>0</v>
+      </c>
+      <c r="AD70" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="71" spans="1:30">
+      <c r="A71" s="1">
+        <v>53</v>
       </c>
       <c r="B71" s="6">
         <v>100</v>
@@ -4831,10 +7607,40 @@
       <c r="T71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:20">
-      <c r="A72" s="3">
-        <v>45797</v>
+      <c r="U71">
+        <v>0</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>0</v>
+      </c>
+      <c r="X71">
+        <v>0</v>
+      </c>
+      <c r="Y71">
+        <v>0</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+      <c r="AA71">
+        <v>0</v>
+      </c>
+      <c r="AB71">
+        <v>0</v>
+      </c>
+      <c r="AC71">
+        <v>0</v>
+      </c>
+      <c r="AD71" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="72" spans="1:30">
+      <c r="A72" s="1">
+        <v>32</v>
       </c>
       <c r="B72" s="6">
         <v>100</v>
@@ -4893,10 +7699,40 @@
       <c r="T72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:20">
-      <c r="A73" s="3">
-        <v>45798</v>
+      <c r="U72">
+        <v>0</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>0</v>
+      </c>
+      <c r="X72">
+        <v>0</v>
+      </c>
+      <c r="Y72">
+        <v>0</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+      <c r="AA72">
+        <v>0</v>
+      </c>
+      <c r="AB72">
+        <v>0</v>
+      </c>
+      <c r="AC72">
+        <v>0</v>
+      </c>
+      <c r="AD72" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="73" spans="1:30">
+      <c r="A73" s="1">
+        <v>91</v>
       </c>
       <c r="B73" s="6">
         <v>100</v>
@@ -4955,10 +7791,40 @@
       <c r="T73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:20">
-      <c r="A74" s="3">
-        <v>45799</v>
+      <c r="U73">
+        <v>0</v>
+      </c>
+      <c r="V73">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>0</v>
+      </c>
+      <c r="X73">
+        <v>0</v>
+      </c>
+      <c r="Y73">
+        <v>0</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+      <c r="AA73">
+        <v>0</v>
+      </c>
+      <c r="AB73">
+        <v>0</v>
+      </c>
+      <c r="AC73">
+        <v>0</v>
+      </c>
+      <c r="AD73" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="74" spans="1:30">
+      <c r="A74" s="1">
+        <v>92</v>
       </c>
       <c r="B74" s="6">
         <v>100</v>
@@ -5017,10 +7883,40 @@
       <c r="T74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:20">
-      <c r="A75" s="3">
-        <v>45800</v>
+      <c r="U74">
+        <v>0</v>
+      </c>
+      <c r="V74">
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <v>0</v>
+      </c>
+      <c r="X74">
+        <v>0</v>
+      </c>
+      <c r="Y74">
+        <v>0</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+      <c r="AA74">
+        <v>0</v>
+      </c>
+      <c r="AB74">
+        <v>0</v>
+      </c>
+      <c r="AC74">
+        <v>0</v>
+      </c>
+      <c r="AD74" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="75" spans="1:30">
+      <c r="A75" s="1">
+        <v>38</v>
       </c>
       <c r="B75" s="6">
         <v>100</v>
@@ -5079,10 +7975,40 @@
       <c r="T75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:20">
-      <c r="A76" s="3">
-        <v>45801</v>
+      <c r="U75">
+        <v>0</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0</v>
+      </c>
+      <c r="X75">
+        <v>0</v>
+      </c>
+      <c r="Y75">
+        <v>0</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+      <c r="AA75">
+        <v>0</v>
+      </c>
+      <c r="AB75">
+        <v>0</v>
+      </c>
+      <c r="AC75">
+        <v>0</v>
+      </c>
+      <c r="AD75" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="76" spans="1:30">
+      <c r="A76" s="1">
+        <v>94</v>
       </c>
       <c r="B76" s="6">
         <v>100</v>
@@ -5141,10 +8067,40 @@
       <c r="T76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:20">
-      <c r="A77" s="3">
-        <v>45803</v>
+      <c r="U76">
+        <v>0</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <v>0</v>
+      </c>
+      <c r="X76">
+        <v>0</v>
+      </c>
+      <c r="Y76">
+        <v>0</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+      <c r="AA76">
+        <v>0</v>
+      </c>
+      <c r="AB76">
+        <v>0</v>
+      </c>
+      <c r="AC76">
+        <v>0</v>
+      </c>
+      <c r="AD76" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="77" spans="1:30">
+      <c r="A77" s="1">
+        <v>9</v>
       </c>
       <c r="B77" s="6">
         <v>100</v>
@@ -5203,10 +8159,40 @@
       <c r="T77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:20">
-      <c r="A78" s="3">
-        <v>45804</v>
+      <c r="U77">
+        <v>0</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0</v>
+      </c>
+      <c r="X77">
+        <v>0</v>
+      </c>
+      <c r="Y77">
+        <v>0</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+      <c r="AA77">
+        <v>0</v>
+      </c>
+      <c r="AB77">
+        <v>0</v>
+      </c>
+      <c r="AC77">
+        <v>0</v>
+      </c>
+      <c r="AD77" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="78" spans="1:30">
+      <c r="A78" s="1">
+        <v>77</v>
       </c>
       <c r="B78" s="6">
         <v>100</v>
@@ -5265,10 +8251,40 @@
       <c r="T78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:20">
-      <c r="A79" s="3">
-        <v>45805</v>
+      <c r="U78">
+        <v>0</v>
+      </c>
+      <c r="V78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>0</v>
+      </c>
+      <c r="X78">
+        <v>0</v>
+      </c>
+      <c r="Y78">
+        <v>0</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+      <c r="AA78">
+        <v>0</v>
+      </c>
+      <c r="AB78">
+        <v>0</v>
+      </c>
+      <c r="AC78">
+        <v>0</v>
+      </c>
+      <c r="AD78" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="79" spans="1:30">
+      <c r="A79" s="1">
+        <v>13</v>
       </c>
       <c r="B79" s="6">
         <v>100</v>
@@ -5327,10 +8343,40 @@
       <c r="T79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:20">
-      <c r="A80" s="3">
-        <v>45806</v>
+      <c r="U79">
+        <v>0</v>
+      </c>
+      <c r="V79">
+        <v>0</v>
+      </c>
+      <c r="W79">
+        <v>0</v>
+      </c>
+      <c r="X79">
+        <v>0</v>
+      </c>
+      <c r="Y79">
+        <v>0</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+      <c r="AA79">
+        <v>0</v>
+      </c>
+      <c r="AB79">
+        <v>0</v>
+      </c>
+      <c r="AC79">
+        <v>0</v>
+      </c>
+      <c r="AD79" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="80" spans="1:30">
+      <c r="A80" s="1">
+        <v>14</v>
       </c>
       <c r="B80" s="6">
         <v>100</v>
@@ -5389,10 +8435,40 @@
       <c r="T80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:20">
-      <c r="A81" s="3">
-        <v>45807</v>
+      <c r="U80">
+        <v>0</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>0</v>
+      </c>
+      <c r="X80">
+        <v>0</v>
+      </c>
+      <c r="Y80">
+        <v>0</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+      <c r="AA80">
+        <v>0</v>
+      </c>
+      <c r="AB80">
+        <v>0</v>
+      </c>
+      <c r="AC80">
+        <v>0</v>
+      </c>
+      <c r="AD80" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="81" spans="1:30">
+      <c r="A81" s="1">
+        <v>22</v>
       </c>
       <c r="B81" s="6">
         <v>100</v>
@@ -5451,10 +8527,40 @@
       <c r="T81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:20">
-      <c r="A82" s="3">
-        <v>45808</v>
+      <c r="U81">
+        <v>0</v>
+      </c>
+      <c r="V81">
+        <v>0</v>
+      </c>
+      <c r="W81">
+        <v>0</v>
+      </c>
+      <c r="X81">
+        <v>0</v>
+      </c>
+      <c r="Y81">
+        <v>0</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+      <c r="AA81">
+        <v>0</v>
+      </c>
+      <c r="AB81">
+        <v>0</v>
+      </c>
+      <c r="AC81">
+        <v>0</v>
+      </c>
+      <c r="AD81" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="82" spans="1:30">
+      <c r="A82" s="1">
+        <v>21</v>
       </c>
       <c r="B82" s="6">
         <v>100</v>
@@ -5513,10 +8619,40 @@
       <c r="T82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:20">
-      <c r="A83" s="3">
-        <v>45810</v>
+      <c r="U82">
+        <v>0</v>
+      </c>
+      <c r="V82">
+        <v>0</v>
+      </c>
+      <c r="W82">
+        <v>0</v>
+      </c>
+      <c r="X82">
+        <v>0</v>
+      </c>
+      <c r="Y82">
+        <v>0</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+      <c r="AA82">
+        <v>0</v>
+      </c>
+      <c r="AB82">
+        <v>0</v>
+      </c>
+      <c r="AC82">
+        <v>0</v>
+      </c>
+      <c r="AD82" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="83" spans="1:30">
+      <c r="A83" s="1">
+        <v>56</v>
       </c>
       <c r="B83" s="6">
         <v>100</v>
@@ -5575,10 +8711,40 @@
       <c r="T83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:20">
-      <c r="A84" s="3">
-        <v>45811</v>
+      <c r="U83">
+        <v>0</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+      <c r="W83">
+        <v>0</v>
+      </c>
+      <c r="X83">
+        <v>0</v>
+      </c>
+      <c r="Y83">
+        <v>0</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+      <c r="AA83">
+        <v>0</v>
+      </c>
+      <c r="AB83">
+        <v>0</v>
+      </c>
+      <c r="AC83">
+        <v>0</v>
+      </c>
+      <c r="AD83" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="84" spans="1:30">
+      <c r="A84" s="1">
+        <v>59</v>
       </c>
       <c r="B84" s="6">
         <v>100</v>
@@ -5637,10 +8803,40 @@
       <c r="T84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:20">
-      <c r="A85" s="3">
-        <v>45812</v>
+      <c r="U84">
+        <v>0</v>
+      </c>
+      <c r="V84">
+        <v>0</v>
+      </c>
+      <c r="W84">
+        <v>0</v>
+      </c>
+      <c r="X84">
+        <v>0</v>
+      </c>
+      <c r="Y84">
+        <v>0</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+      <c r="AA84">
+        <v>0</v>
+      </c>
+      <c r="AB84">
+        <v>0</v>
+      </c>
+      <c r="AC84">
+        <v>0</v>
+      </c>
+      <c r="AD84" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="85" spans="1:30">
+      <c r="A85" s="1">
+        <v>64</v>
       </c>
       <c r="B85" s="6">
         <v>100</v>
@@ -5699,10 +8895,40 @@
       <c r="T85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:20">
-      <c r="A86" s="3">
-        <v>45813</v>
+      <c r="U85">
+        <v>0</v>
+      </c>
+      <c r="V85">
+        <v>0</v>
+      </c>
+      <c r="W85">
+        <v>0</v>
+      </c>
+      <c r="X85">
+        <v>0</v>
+      </c>
+      <c r="Y85">
+        <v>0</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+      <c r="AA85">
+        <v>0</v>
+      </c>
+      <c r="AB85">
+        <v>0</v>
+      </c>
+      <c r="AC85">
+        <v>0</v>
+      </c>
+      <c r="AD85" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="86" spans="1:30">
+      <c r="A86" s="1">
+        <v>18</v>
       </c>
       <c r="B86" s="6">
         <v>100</v>
@@ -5761,10 +8987,40 @@
       <c r="T86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:20">
-      <c r="A87" s="3">
-        <v>45814</v>
+      <c r="U86">
+        <v>0</v>
+      </c>
+      <c r="V86">
+        <v>0</v>
+      </c>
+      <c r="W86">
+        <v>0</v>
+      </c>
+      <c r="X86">
+        <v>0</v>
+      </c>
+      <c r="Y86">
+        <v>0</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+      <c r="AA86">
+        <v>0</v>
+      </c>
+      <c r="AB86">
+        <v>0</v>
+      </c>
+      <c r="AC86">
+        <v>0</v>
+      </c>
+      <c r="AD86" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="87" spans="1:30">
+      <c r="A87" s="1">
+        <v>69</v>
       </c>
       <c r="B87" s="6">
         <v>100</v>
@@ -5823,10 +9079,40 @@
       <c r="T87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:20">
-      <c r="A88" s="3">
-        <v>45815</v>
+      <c r="U87">
+        <v>0</v>
+      </c>
+      <c r="V87">
+        <v>0</v>
+      </c>
+      <c r="W87">
+        <v>0</v>
+      </c>
+      <c r="X87">
+        <v>0</v>
+      </c>
+      <c r="Y87">
+        <v>0</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+      <c r="AA87">
+        <v>0</v>
+      </c>
+      <c r="AB87">
+        <v>0</v>
+      </c>
+      <c r="AC87">
+        <v>0</v>
+      </c>
+      <c r="AD87" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="88" spans="1:30">
+      <c r="A88" s="1">
+        <v>72</v>
       </c>
       <c r="B88" s="6">
         <v>100</v>
@@ -5885,10 +9171,40 @@
       <c r="T88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:20">
-      <c r="A89" s="3">
-        <v>45817</v>
+      <c r="U88">
+        <v>0</v>
+      </c>
+      <c r="V88">
+        <v>0</v>
+      </c>
+      <c r="W88">
+        <v>0</v>
+      </c>
+      <c r="X88">
+        <v>0</v>
+      </c>
+      <c r="Y88">
+        <v>0</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+      <c r="AA88">
+        <v>0</v>
+      </c>
+      <c r="AB88">
+        <v>0</v>
+      </c>
+      <c r="AC88">
+        <v>0</v>
+      </c>
+      <c r="AD88" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="89" spans="1:30">
+      <c r="A89" s="1">
+        <v>24</v>
       </c>
       <c r="B89" s="6">
         <v>100</v>
@@ -5947,10 +9263,40 @@
       <c r="T89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:20">
-      <c r="A90" s="3">
-        <v>45818</v>
+      <c r="U89">
+        <v>0</v>
+      </c>
+      <c r="V89">
+        <v>0</v>
+      </c>
+      <c r="W89">
+        <v>0</v>
+      </c>
+      <c r="X89">
+        <v>0</v>
+      </c>
+      <c r="Y89">
+        <v>0</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+      <c r="AA89">
+        <v>0</v>
+      </c>
+      <c r="AB89">
+        <v>0</v>
+      </c>
+      <c r="AC89">
+        <v>0</v>
+      </c>
+      <c r="AD89" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="90" spans="1:30">
+      <c r="A90" s="1">
+        <v>34</v>
       </c>
       <c r="B90" s="6">
         <v>100</v>
@@ -6009,10 +9355,40 @@
       <c r="T90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:20">
-      <c r="A91" s="3">
-        <v>45819</v>
+      <c r="U90">
+        <v>0</v>
+      </c>
+      <c r="V90">
+        <v>0</v>
+      </c>
+      <c r="W90">
+        <v>0</v>
+      </c>
+      <c r="X90">
+        <v>0</v>
+      </c>
+      <c r="Y90">
+        <v>0</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+      <c r="AA90">
+        <v>0</v>
+      </c>
+      <c r="AB90">
+        <v>0</v>
+      </c>
+      <c r="AC90">
+        <v>0</v>
+      </c>
+      <c r="AD90" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="91" spans="1:30">
+      <c r="A91" s="1">
+        <v>65</v>
       </c>
       <c r="B91" s="6">
         <v>100</v>
@@ -6071,10 +9447,40 @@
       <c r="T91">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:20">
-      <c r="A92" s="3">
-        <v>45820</v>
+      <c r="U91">
+        <v>0</v>
+      </c>
+      <c r="V91">
+        <v>0</v>
+      </c>
+      <c r="W91">
+        <v>0</v>
+      </c>
+      <c r="X91">
+        <v>0</v>
+      </c>
+      <c r="Y91">
+        <v>0</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+      <c r="AA91">
+        <v>0</v>
+      </c>
+      <c r="AB91">
+        <v>0</v>
+      </c>
+      <c r="AC91">
+        <v>0</v>
+      </c>
+      <c r="AD91" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="92" spans="1:30">
+      <c r="A92" s="1">
+        <v>29</v>
       </c>
       <c r="B92" s="6">
         <v>100</v>
@@ -6133,10 +9539,40 @@
       <c r="T92">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:20">
-      <c r="A93" s="3">
-        <v>45821</v>
+      <c r="U92">
+        <v>0</v>
+      </c>
+      <c r="V92">
+        <v>0</v>
+      </c>
+      <c r="W92">
+        <v>0</v>
+      </c>
+      <c r="X92">
+        <v>0</v>
+      </c>
+      <c r="Y92">
+        <v>0</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+      <c r="AA92">
+        <v>0</v>
+      </c>
+      <c r="AB92">
+        <v>0</v>
+      </c>
+      <c r="AC92">
+        <v>0</v>
+      </c>
+      <c r="AD92" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="93" spans="1:30">
+      <c r="A93" s="1">
+        <v>8</v>
       </c>
       <c r="B93" s="6">
         <v>100</v>
@@ -6195,10 +9631,40 @@
       <c r="T93">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:20">
-      <c r="A94" s="3">
-        <v>45822</v>
+      <c r="U93">
+        <v>0</v>
+      </c>
+      <c r="V93">
+        <v>0</v>
+      </c>
+      <c r="W93">
+        <v>0</v>
+      </c>
+      <c r="X93">
+        <v>0</v>
+      </c>
+      <c r="Y93">
+        <v>0</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+      <c r="AA93">
+        <v>0</v>
+      </c>
+      <c r="AB93">
+        <v>0</v>
+      </c>
+      <c r="AC93">
+        <v>0</v>
+      </c>
+      <c r="AD93" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="94" spans="1:30">
+      <c r="A94" s="1">
+        <v>68</v>
       </c>
       <c r="B94" s="6">
         <v>100</v>
@@ -6257,10 +9723,40 @@
       <c r="T94">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:20">
-      <c r="A95" s="3">
-        <v>45824</v>
+      <c r="U94">
+        <v>0</v>
+      </c>
+      <c r="V94">
+        <v>0</v>
+      </c>
+      <c r="W94">
+        <v>0</v>
+      </c>
+      <c r="X94">
+        <v>0</v>
+      </c>
+      <c r="Y94">
+        <v>0</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+      <c r="AA94">
+        <v>0</v>
+      </c>
+      <c r="AB94">
+        <v>0</v>
+      </c>
+      <c r="AC94">
+        <v>0</v>
+      </c>
+      <c r="AD94" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="95" spans="1:30">
+      <c r="A95" s="1">
+        <v>23</v>
       </c>
       <c r="B95" s="6">
         <v>100</v>
@@ -6319,10 +9815,40 @@
       <c r="T95">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:20">
-      <c r="A96" s="3">
-        <v>45825</v>
+      <c r="U95">
+        <v>0</v>
+      </c>
+      <c r="V95">
+        <v>0</v>
+      </c>
+      <c r="W95">
+        <v>0</v>
+      </c>
+      <c r="X95">
+        <v>0</v>
+      </c>
+      <c r="Y95">
+        <v>0</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+      <c r="AA95">
+        <v>0</v>
+      </c>
+      <c r="AB95">
+        <v>0</v>
+      </c>
+      <c r="AC95">
+        <v>0</v>
+      </c>
+      <c r="AD95" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="96" spans="1:30">
+      <c r="A96" s="1">
+        <v>7</v>
       </c>
       <c r="B96" s="6">
         <v>100</v>
@@ -6381,10 +9907,40 @@
       <c r="T96">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:20">
-      <c r="A97" s="3">
-        <v>45826</v>
+      <c r="U96">
+        <v>0</v>
+      </c>
+      <c r="V96">
+        <v>0</v>
+      </c>
+      <c r="W96">
+        <v>0</v>
+      </c>
+      <c r="X96">
+        <v>0</v>
+      </c>
+      <c r="Y96">
+        <v>0</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+      <c r="AA96">
+        <v>0</v>
+      </c>
+      <c r="AB96">
+        <v>0</v>
+      </c>
+      <c r="AC96">
+        <v>0</v>
+      </c>
+      <c r="AD96" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="97" spans="1:30">
+      <c r="A97" s="1">
+        <v>62</v>
       </c>
       <c r="B97" s="6">
         <v>100</v>
@@ -6443,10 +9999,40 @@
       <c r="T97">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:20">
-      <c r="A98" s="3">
-        <v>45827</v>
+      <c r="U97">
+        <v>0</v>
+      </c>
+      <c r="V97">
+        <v>0</v>
+      </c>
+      <c r="W97">
+        <v>0</v>
+      </c>
+      <c r="X97">
+        <v>0</v>
+      </c>
+      <c r="Y97">
+        <v>0</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+      <c r="AA97">
+        <v>0</v>
+      </c>
+      <c r="AB97">
+        <v>0</v>
+      </c>
+      <c r="AC97">
+        <v>0</v>
+      </c>
+      <c r="AD97" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="98" spans="1:30">
+      <c r="A98" s="1">
+        <v>51</v>
       </c>
       <c r="B98" s="6">
         <v>100</v>
@@ -6505,10 +10091,40 @@
       <c r="T98">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:20">
-      <c r="A99" s="3">
-        <v>45828</v>
+      <c r="U98">
+        <v>0</v>
+      </c>
+      <c r="V98">
+        <v>0</v>
+      </c>
+      <c r="W98">
+        <v>0</v>
+      </c>
+      <c r="X98">
+        <v>0</v>
+      </c>
+      <c r="Y98">
+        <v>0</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+      <c r="AA98">
+        <v>0</v>
+      </c>
+      <c r="AB98">
+        <v>0</v>
+      </c>
+      <c r="AC98">
+        <v>0</v>
+      </c>
+      <c r="AD98" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="99" spans="1:30">
+      <c r="A99" s="1">
+        <v>82</v>
       </c>
       <c r="B99" s="6">
         <v>100</v>
@@ -6567,10 +10183,40 @@
       <c r="T99">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:20">
-      <c r="A100" s="3">
-        <v>45829</v>
+      <c r="U99">
+        <v>0</v>
+      </c>
+      <c r="V99">
+        <v>0</v>
+      </c>
+      <c r="W99">
+        <v>0</v>
+      </c>
+      <c r="X99">
+        <v>0</v>
+      </c>
+      <c r="Y99">
+        <v>0</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+      <c r="AA99">
+        <v>0</v>
+      </c>
+      <c r="AB99">
+        <v>0</v>
+      </c>
+      <c r="AC99">
+        <v>0</v>
+      </c>
+      <c r="AD99" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="100" spans="1:30">
+      <c r="A100" s="1">
+        <v>58</v>
       </c>
       <c r="B100" s="7">
         <v>100</v>
@@ -6629,10 +10275,40 @@
       <c r="T100">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:20">
-      <c r="A101" s="3">
-        <v>45831</v>
+      <c r="U100">
+        <v>0</v>
+      </c>
+      <c r="V100">
+        <v>0</v>
+      </c>
+      <c r="W100">
+        <v>0</v>
+      </c>
+      <c r="X100">
+        <v>0</v>
+      </c>
+      <c r="Y100">
+        <v>0</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+      <c r="AA100">
+        <v>0</v>
+      </c>
+      <c r="AB100">
+        <v>0</v>
+      </c>
+      <c r="AC100">
+        <v>0</v>
+      </c>
+      <c r="AD100" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="101" spans="1:30">
+      <c r="A101" s="1">
+        <v>70</v>
       </c>
       <c r="B101" s="7">
         <v>100</v>
@@ -6691,10 +10367,40 @@
       <c r="T101">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:20">
-      <c r="A102" s="3">
-        <v>45832</v>
+      <c r="U101">
+        <v>0</v>
+      </c>
+      <c r="V101">
+        <v>0</v>
+      </c>
+      <c r="W101">
+        <v>0</v>
+      </c>
+      <c r="X101">
+        <v>0</v>
+      </c>
+      <c r="Y101">
+        <v>0</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
+      </c>
+      <c r="AA101">
+        <v>0</v>
+      </c>
+      <c r="AB101">
+        <v>0</v>
+      </c>
+      <c r="AC101">
+        <v>0</v>
+      </c>
+      <c r="AD101" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="102" spans="1:30">
+      <c r="A102" s="1">
+        <v>35</v>
       </c>
       <c r="B102" s="7">
         <v>100</v>
@@ -6753,9 +10459,39 @@
       <c r="T102">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:20">
-      <c r="A103" s="3">
+      <c r="U102">
+        <v>0</v>
+      </c>
+      <c r="V102">
+        <v>0</v>
+      </c>
+      <c r="W102">
+        <v>0</v>
+      </c>
+      <c r="X102">
+        <v>0</v>
+      </c>
+      <c r="Y102">
+        <v>0</v>
+      </c>
+      <c r="Z102">
+        <v>0</v>
+      </c>
+      <c r="AA102">
+        <v>0</v>
+      </c>
+      <c r="AB102">
+        <v>0</v>
+      </c>
+      <c r="AC102">
+        <v>0</v>
+      </c>
+      <c r="AD102" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="103" spans="1:30">
+      <c r="A103" s="10">
         <v>45833</v>
       </c>
       <c r="B103" s="7">
@@ -6816,8 +10552,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:20">
-      <c r="A104" s="3">
+    <row r="104" spans="1:30">
+      <c r="A104" s="10">
         <v>45834</v>
       </c>
       <c r="B104" s="7">
@@ -6878,8 +10614,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:20">
-      <c r="A105" s="3">
+    <row r="105" spans="1:30">
+      <c r="A105" s="10">
         <v>45835</v>
       </c>
       <c r="B105" s="7">
@@ -6940,8 +10676,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:20">
-      <c r="A106" s="3">
+    <row r="106" spans="1:30">
+      <c r="A106" s="10">
         <v>45836</v>
       </c>
       <c r="B106" s="7">
@@ -7002,8 +10738,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:20">
-      <c r="A107" s="3">
+    <row r="107" spans="1:30">
+      <c r="A107" s="10">
         <v>45838</v>
       </c>
       <c r="B107" s="7">
@@ -7064,8 +10800,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:20">
-      <c r="A108" s="3">
+    <row r="108" spans="1:30">
+      <c r="A108" s="10">
         <v>45839</v>
       </c>
       <c r="B108" s="7">
@@ -7126,8 +10862,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:20">
-      <c r="A109" s="3">
+    <row r="109" spans="1:30">
+      <c r="A109" s="10">
         <v>45840</v>
       </c>
       <c r="B109" s="7">
@@ -7188,8 +10924,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:20">
-      <c r="A110" s="3">
+    <row r="110" spans="1:30">
+      <c r="A110" s="10">
         <v>45841</v>
       </c>
       <c r="B110" s="7">
@@ -7250,8 +10986,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:20">
-      <c r="A111" s="3">
+    <row r="111" spans="1:30">
+      <c r="A111" s="10">
         <v>45842</v>
       </c>
       <c r="B111" s="7">
@@ -7312,8 +11048,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:20">
-      <c r="A112" s="3">
+    <row r="112" spans="1:30">
+      <c r="A112" s="10">
         <v>45843</v>
       </c>
       <c r="B112" s="7">
@@ -7375,7 +11111,7 @@
       </c>
     </row>
     <row r="113" spans="1:20">
-      <c r="A113" s="3">
+      <c r="A113" s="10">
         <v>45845</v>
       </c>
       <c r="B113" s="7">
@@ -7437,7 +11173,7 @@
       </c>
     </row>
     <row r="114" spans="1:20">
-      <c r="A114" s="3">
+      <c r="A114" s="10">
         <v>45846</v>
       </c>
       <c r="B114" s="7">
@@ -7499,7 +11235,7 @@
       </c>
     </row>
     <row r="115" spans="1:20">
-      <c r="A115" s="3">
+      <c r="A115" s="10">
         <v>45847</v>
       </c>
       <c r="B115" s="7">
@@ -7561,7 +11297,7 @@
       </c>
     </row>
     <row r="116" spans="1:20">
-      <c r="A116" s="3">
+      <c r="A116" s="10">
         <v>45848</v>
       </c>
       <c r="B116" s="7">
@@ -7623,7 +11359,7 @@
       </c>
     </row>
     <row r="117" spans="1:20">
-      <c r="A117" s="3">
+      <c r="A117" s="10">
         <v>45849</v>
       </c>
       <c r="B117" s="7">
@@ -7685,7 +11421,7 @@
       </c>
     </row>
     <row r="118" spans="1:20">
-      <c r="A118" s="3">
+      <c r="A118" s="10">
         <v>45850</v>
       </c>
       <c r="B118" s="7">
@@ -7747,7 +11483,7 @@
       </c>
     </row>
     <row r="119" spans="1:20">
-      <c r="A119" s="3">
+      <c r="A119" s="10">
         <v>45852</v>
       </c>
       <c r="B119" s="8">
@@ -7809,7 +11545,7 @@
       </c>
     </row>
     <row r="120" spans="1:20">
-      <c r="A120" s="3">
+      <c r="A120" s="10">
         <v>45853</v>
       </c>
       <c r="B120" s="8">
@@ -7871,7 +11607,7 @@
       </c>
     </row>
     <row r="121" spans="1:20">
-      <c r="A121" s="3">
+      <c r="A121" s="10">
         <v>45854</v>
       </c>
       <c r="B121" s="8">
@@ -7933,7 +11669,7 @@
       </c>
     </row>
     <row r="122" spans="1:20">
-      <c r="A122" s="3">
+      <c r="A122" s="10">
         <v>45855</v>
       </c>
       <c r="B122" s="8">
@@ -7995,7 +11731,7 @@
       </c>
     </row>
     <row r="123" spans="1:20">
-      <c r="A123" s="3">
+      <c r="A123" s="10">
         <v>45856</v>
       </c>
       <c r="B123" s="8">
@@ -8057,7 +11793,7 @@
       </c>
     </row>
     <row r="124" spans="1:20">
-      <c r="A124" s="3">
+      <c r="A124" s="10">
         <v>45857</v>
       </c>
       <c r="B124" s="8">
@@ -8119,7 +11855,7 @@
       </c>
     </row>
     <row r="125" spans="1:20">
-      <c r="A125" s="3">
+      <c r="A125" s="10">
         <v>45859</v>
       </c>
       <c r="B125" s="8">
@@ -8181,7 +11917,7 @@
       </c>
     </row>
     <row r="126" spans="1:20">
-      <c r="A126" s="3">
+      <c r="A126" s="10">
         <v>45860</v>
       </c>
       <c r="B126" s="8">
@@ -8243,7 +11979,7 @@
       </c>
     </row>
     <row r="127" spans="1:20">
-      <c r="A127" s="3">
+      <c r="A127" s="10">
         <v>45861</v>
       </c>
       <c r="B127" s="8">
@@ -8305,7 +12041,7 @@
       </c>
     </row>
     <row r="128" spans="1:20">
-      <c r="A128" s="3">
+      <c r="A128" s="10">
         <v>45862</v>
       </c>
       <c r="B128" s="8">
@@ -8367,7 +12103,7 @@
       </c>
     </row>
     <row r="129" spans="1:20">
-      <c r="A129" s="3">
+      <c r="A129" s="10">
         <v>45863</v>
       </c>
       <c r="B129" s="8">
@@ -8429,7 +12165,7 @@
       </c>
     </row>
     <row r="130" spans="1:20">
-      <c r="A130" s="3">
+      <c r="A130" s="10">
         <v>45864</v>
       </c>
       <c r="B130" s="8">
@@ -8491,7 +12227,7 @@
       </c>
     </row>
     <row r="131" spans="1:20">
-      <c r="A131" s="3">
+      <c r="A131" s="10">
         <v>45866</v>
       </c>
       <c r="B131" s="8">
@@ -8553,7 +12289,7 @@
       </c>
     </row>
     <row r="132" spans="1:20">
-      <c r="A132" s="3">
+      <c r="A132" s="10">
         <v>45867</v>
       </c>
       <c r="B132" s="8">
@@ -8615,7 +12351,7 @@
       </c>
     </row>
     <row r="133" spans="1:20">
-      <c r="A133" s="3">
+      <c r="A133" s="10">
         <v>45868</v>
       </c>
       <c r="B133" s="8">
@@ -8677,7 +12413,7 @@
       </c>
     </row>
     <row r="134" spans="1:20">
-      <c r="A134" s="3">
+      <c r="A134" s="10">
         <v>45869</v>
       </c>
       <c r="B134" s="8">
@@ -8739,7 +12475,7 @@
       </c>
     </row>
     <row r="135" spans="1:20">
-      <c r="A135" s="3">
+      <c r="A135" s="10">
         <v>45870</v>
       </c>
       <c r="B135" s="8">
@@ -8801,7 +12537,7 @@
       </c>
     </row>
     <row r="136" spans="1:20">
-      <c r="A136" s="3">
+      <c r="A136" s="10">
         <v>45871</v>
       </c>
       <c r="B136" s="8">
@@ -8863,7 +12599,7 @@
       </c>
     </row>
     <row r="137" spans="1:20">
-      <c r="A137" s="3">
+      <c r="A137" s="10">
         <v>45873</v>
       </c>
       <c r="B137" s="8">
@@ -8925,7 +12661,7 @@
       </c>
     </row>
     <row r="138" spans="1:20">
-      <c r="A138" s="3">
+      <c r="A138" s="10">
         <v>45874</v>
       </c>
       <c r="B138" s="8">
@@ -8987,7 +12723,7 @@
       </c>
     </row>
     <row r="139" spans="1:20">
-      <c r="A139" s="3">
+      <c r="A139" s="10">
         <v>45875</v>
       </c>
       <c r="B139" s="8">
@@ -9049,7 +12785,7 @@
       </c>
     </row>
     <row r="140" spans="1:20">
-      <c r="A140" s="3">
+      <c r="A140" s="10">
         <v>45876</v>
       </c>
       <c r="B140" s="8">
@@ -9111,7 +12847,7 @@
       </c>
     </row>
     <row r="141" spans="1:20">
-      <c r="A141" s="3">
+      <c r="A141" s="10">
         <v>45877</v>
       </c>
       <c r="B141" s="8">
@@ -9173,7 +12909,7 @@
       </c>
     </row>
     <row r="142" spans="1:20">
-      <c r="A142" s="3">
+      <c r="A142" s="10">
         <v>45878</v>
       </c>
       <c r="B142" s="8">
@@ -9235,7 +12971,7 @@
       </c>
     </row>
     <row r="143" spans="1:20">
-      <c r="A143" s="3">
+      <c r="A143" s="10">
         <v>45880</v>
       </c>
       <c r="B143" s="8">
@@ -9297,7 +13033,7 @@
       </c>
     </row>
     <row r="144" spans="1:20">
-      <c r="A144" s="3">
+      <c r="A144" s="10">
         <v>45881</v>
       </c>
       <c r="B144" s="8">
@@ -9359,7 +13095,7 @@
       </c>
     </row>
     <row r="145" spans="1:20">
-      <c r="A145" s="3">
+      <c r="A145" s="10">
         <v>45882</v>
       </c>
       <c r="B145" s="8">
@@ -9421,7 +13157,7 @@
       </c>
     </row>
     <row r="146" spans="1:20">
-      <c r="A146" s="3">
+      <c r="A146" s="10">
         <v>45883</v>
       </c>
       <c r="B146" s="8">
@@ -9483,7 +13219,7 @@
       </c>
     </row>
     <row r="147" spans="1:20">
-      <c r="A147" s="3">
+      <c r="A147" s="10">
         <v>45884</v>
       </c>
       <c r="B147" s="8">
@@ -9545,7 +13281,7 @@
       </c>
     </row>
     <row r="148" spans="1:20">
-      <c r="A148" s="3">
+      <c r="A148" s="10">
         <v>45885</v>
       </c>
       <c r="B148" s="8">
@@ -9607,7 +13343,7 @@
       </c>
     </row>
     <row r="149" spans="1:20">
-      <c r="A149" s="3">
+      <c r="A149" s="10">
         <v>45887</v>
       </c>
       <c r="B149" s="8">
@@ -9669,7 +13405,7 @@
       </c>
     </row>
     <row r="150" spans="1:20">
-      <c r="A150" s="3">
+      <c r="A150" s="10">
         <v>45888</v>
       </c>
       <c r="B150" s="8">
@@ -9731,7 +13467,7 @@
       </c>
     </row>
     <row r="151" spans="1:20">
-      <c r="A151" s="3">
+      <c r="A151" s="10">
         <v>45889</v>
       </c>
       <c r="B151" s="8">
@@ -9793,7 +13529,7 @@
       </c>
     </row>
     <row r="152" spans="1:20">
-      <c r="A152" s="3">
+      <c r="A152" s="10">
         <v>45890</v>
       </c>
       <c r="B152" s="8">
@@ -9855,7 +13591,7 @@
       </c>
     </row>
     <row r="153" spans="1:20">
-      <c r="A153" s="3">
+      <c r="A153" s="10">
         <v>45891</v>
       </c>
       <c r="B153" s="8">
@@ -9917,7 +13653,7 @@
       </c>
     </row>
     <row r="154" spans="1:20">
-      <c r="A154" s="3">
+      <c r="A154" s="10">
         <v>45892</v>
       </c>
       <c r="B154" s="8">
@@ -9979,7 +13715,7 @@
       </c>
     </row>
     <row r="155" spans="1:20">
-      <c r="A155" s="3">
+      <c r="A155" s="10">
         <v>45894</v>
       </c>
       <c r="B155" s="9">
@@ -10041,7 +13777,7 @@
       </c>
     </row>
     <row r="156" spans="1:20">
-      <c r="A156" s="3">
+      <c r="A156" s="10">
         <v>45895</v>
       </c>
       <c r="B156" s="9">
@@ -10103,7 +13839,7 @@
       </c>
     </row>
     <row r="157" spans="1:20">
-      <c r="A157" s="3">
+      <c r="A157" s="10">
         <v>45896</v>
       </c>
       <c r="B157" s="9">
@@ -10165,7 +13901,7 @@
       </c>
     </row>
     <row r="158" spans="1:20">
-      <c r="A158" s="3">
+      <c r="A158" s="10">
         <v>45897</v>
       </c>
       <c r="B158" s="9">
@@ -10227,7 +13963,7 @@
       </c>
     </row>
     <row r="159" spans="1:20">
-      <c r="A159" s="3">
+      <c r="A159" s="10">
         <v>45898</v>
       </c>
       <c r="B159" s="9">
@@ -10289,7 +14025,7 @@
       </c>
     </row>
     <row r="160" spans="1:20">
-      <c r="A160" s="3">
+      <c r="A160" s="10">
         <v>45899</v>
       </c>
       <c r="B160" s="9">
@@ -10351,7 +14087,7 @@
       </c>
     </row>
     <row r="161" spans="1:20">
-      <c r="A161" s="3">
+      <c r="A161" s="10">
         <v>45901</v>
       </c>
       <c r="B161" s="9">
@@ -10413,7 +14149,7 @@
       </c>
     </row>
     <row r="162" spans="1:20">
-      <c r="A162" s="3">
+      <c r="A162" s="10">
         <v>45902</v>
       </c>
       <c r="B162" s="9">
@@ -10475,7 +14211,7 @@
       </c>
     </row>
     <row r="163" spans="1:20">
-      <c r="A163" s="3">
+      <c r="A163" s="10">
         <v>45903</v>
       </c>
       <c r="B163" s="9">
@@ -10537,7 +14273,7 @@
       </c>
     </row>
     <row r="164" spans="1:20">
-      <c r="A164" s="3">
+      <c r="A164" s="10">
         <v>45904</v>
       </c>
       <c r="B164" s="9">
@@ -10599,7 +14335,7 @@
       </c>
     </row>
     <row r="165" spans="1:20">
-      <c r="A165" s="3">
+      <c r="A165" s="10">
         <v>45905</v>
       </c>
       <c r="B165" s="9">
@@ -10661,7 +14397,7 @@
       </c>
     </row>
     <row r="166" spans="1:20">
-      <c r="A166" s="3">
+      <c r="A166" s="10">
         <v>45906</v>
       </c>
       <c r="B166" s="9">
@@ -10723,7 +14459,7 @@
       </c>
     </row>
     <row r="167" spans="1:20">
-      <c r="A167" s="3">
+      <c r="A167" s="10">
         <v>45908</v>
       </c>
       <c r="B167" s="9">
@@ -10785,7 +14521,7 @@
       </c>
     </row>
     <row r="168" spans="1:20">
-      <c r="A168" s="3">
+      <c r="A168" s="10">
         <v>45909</v>
       </c>
       <c r="B168" s="9">
@@ -10847,7 +14583,7 @@
       </c>
     </row>
     <row r="169" spans="1:20">
-      <c r="A169" s="3">
+      <c r="A169" s="10">
         <v>45910</v>
       </c>
       <c r="B169" s="9">
@@ -10909,7 +14645,7 @@
       </c>
     </row>
     <row r="170" spans="1:20">
-      <c r="A170" s="3">
+      <c r="A170" s="10">
         <v>45911</v>
       </c>
       <c r="B170" s="9">
@@ -10971,7 +14707,7 @@
       </c>
     </row>
     <row r="171" spans="1:20">
-      <c r="A171" s="3">
+      <c r="A171" s="10">
         <v>45912</v>
       </c>
       <c r="B171" s="9">
@@ -11033,7 +14769,7 @@
       </c>
     </row>
     <row r="172" spans="1:20">
-      <c r="A172" s="3">
+      <c r="A172" s="10">
         <v>45913</v>
       </c>
       <c r="B172" s="9">
@@ -11095,7 +14831,7 @@
       </c>
     </row>
     <row r="173" spans="1:20">
-      <c r="A173" s="3">
+      <c r="A173" s="10">
         <v>45915</v>
       </c>
       <c r="B173" s="9">
@@ -11157,7 +14893,7 @@
       </c>
     </row>
     <row r="174" spans="1:20">
-      <c r="A174" s="3">
+      <c r="A174" s="10">
         <v>45916</v>
       </c>
       <c r="B174" s="9">
@@ -11219,7 +14955,7 @@
       </c>
     </row>
     <row r="175" spans="1:20">
-      <c r="A175" s="3">
+      <c r="A175" s="10">
         <v>45917</v>
       </c>
       <c r="B175" s="9">
@@ -11281,7 +15017,7 @@
       </c>
     </row>
     <row r="176" spans="1:20">
-      <c r="A176" s="3">
+      <c r="A176" s="10">
         <v>45918</v>
       </c>
       <c r="B176" s="9">
@@ -11343,7 +15079,7 @@
       </c>
     </row>
     <row r="177" spans="1:20">
-      <c r="A177" s="3">
+      <c r="A177" s="10">
         <v>45919</v>
       </c>
       <c r="B177">
